--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134493951</v>
+        <v>136707324</v>
       </c>
       <c r="B10" t="n">
-        <v>5181</v>
+        <v>4777</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,21 +1570,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325037</v>
+        <v>325067</v>
       </c>
       <c r="R10" t="n">
-        <v>6557099</v>
+        <v>6557022</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,12 +1629,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,50 +1675,46 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493951</t>
+          <t>https://artportalen.se/Sighting/136707324</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134246361</v>
+        <v>134493951</v>
       </c>
       <c r="B11" t="n">
-        <v>5484</v>
+        <v>5181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101920</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -1728,10 +1724,10 @@
         <v>325037</v>
       </c>
       <c r="R11" t="n">
-        <v>6556902</v>
+        <v>6557099</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1755,17 +1751,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,31 +1765,45 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246361</t>
+          <t>https://artportalen.se/Sighting/134493951</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134246677</v>
+        <v>134246361</v>
       </c>
       <c r="B12" t="n">
         <v>5484</v>
@@ -1830,7 +1835,11 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1838,10 +1847,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325095</v>
+        <v>325037</v>
       </c>
       <c r="R12" t="n">
-        <v>6556772</v>
+        <v>6556902</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,7 +1887,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ett kläckhål i tallåga</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1905,13 +1914,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246677</t>
+          <t>https://artportalen.se/Sighting/134246361</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134246697</v>
+        <v>134246677</v>
       </c>
       <c r="B13" t="n">
         <v>5484</v>
@@ -1951,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325058</v>
+        <v>325095</v>
       </c>
       <c r="R13" t="n">
-        <v>6556688</v>
+        <v>6556772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1991,7 +2000,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Kläckhål och gnagspån</t>
+          <t>Ett kläckhål i tallåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,51 +2027,45 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246697</t>
+          <t>https://artportalen.se/Sighting/134246677</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134246438</v>
+        <v>134246697</v>
       </c>
       <c r="B14" t="n">
-        <v>79396</v>
+        <v>5484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>260591</v>
+        <v>101920</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2070,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>325044</v>
+        <v>325058</v>
       </c>
       <c r="R14" t="n">
-        <v>6556865</v>
+        <v>6556688</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,6 +2111,11 @@
           <t>2026-06-08</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnagspån</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2132,13 +2140,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246438</t>
+          <t>https://artportalen.se/Sighting/134246697</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134246734</v>
+        <v>134246438</v>
       </c>
       <c r="B15" t="n">
         <v>79396</v>
@@ -2166,8 +2174,16 @@
           <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2176,10 +2192,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>325035</v>
+        <v>325044</v>
       </c>
       <c r="R15" t="n">
-        <v>6556559</v>
+        <v>6556865</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2214,11 +2230,6 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2242,6 +2253,117 @@
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246438</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134246734</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>325035</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6556559</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134246734</t>
         </is>
@@ -2263,6 +2385,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,51 +797,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133657352</v>
+        <v>136890275</v>
       </c>
       <c r="B3" t="n">
-        <v>93271</v>
+        <v>90859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mellomtjärnet, ca 60 m NO om nordspetsen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>325013</v>
+        <v>325097</v>
       </c>
       <c r="R3" t="n">
-        <v>6556398</v>
+        <v>6556535</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,36 +876,30 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Tallskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657352</t>
+          <t>https://artportalen.se/Sighting/136890275</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133657353</v>
+        <v>133657352</v>
       </c>
       <c r="B4" t="n">
         <v>93271</v>
@@ -942,14 +933,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skacktjärnet, ca 125 m NO om nordspetsen, Dls</t>
+          <t>Mellomtjärnet, ca 60 m NO om nordspetsen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>324949</v>
+        <v>325013</v>
       </c>
       <c r="R4" t="n">
-        <v>6556476</v>
+        <v>6556398</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,13 +1004,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657353</t>
+          <t>https://artportalen.se/Sighting/133657352</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133657355</v>
+        <v>133657353</v>
       </c>
       <c r="B5" t="n">
         <v>93271</v>
@@ -1053,14 +1044,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mellanfjällen, ca 650 m NV om Mardyveln, Dls</t>
+          <t>Skacktjärnet, ca 125 m NO om nordspetsen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325121</v>
+        <v>324949</v>
       </c>
       <c r="R5" t="n">
-        <v>6556881</v>
+        <v>6556476</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,19 +1109,19 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133657355</t>
+          <t>https://artportalen.se/Sighting/133657353</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134246906</v>
+        <v>133657355</v>
       </c>
       <c r="B6" t="n">
         <v>93271</v>
@@ -1164,14 +1155,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svartetjärnen, Dls</t>
+          <t>Mellanfjällen, ca 650 m NV om Mardyveln, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>324955</v>
+        <v>325121</v>
       </c>
       <c r="R6" t="n">
-        <v>6556479</v>
+        <v>6556881</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,17 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,30 +1207,35 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Tallskog.</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Leif Appelgren, Lise Wichmann Hansen, Martin  Sjöberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246906</t>
+          <t>https://artportalen.se/Sighting/133657355</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134246367</v>
+        <v>134246906</v>
       </c>
       <c r="B7" t="n">
-        <v>79992</v>
+        <v>93271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,21 +1243,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,14 +1266,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Svartetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325037</v>
+        <v>324955</v>
       </c>
       <c r="R7" t="n">
-        <v>6556902</v>
+        <v>6556479</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,6 +1308,11 @@
           <t>2026-06-08</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1341,16 +1337,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246367</t>
+          <t>https://artportalen.se/Sighting/134246906</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134246640</v>
+        <v>136890271</v>
       </c>
       <c r="B8" t="n">
-        <v>79992</v>
+        <v>93411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,40 +1354,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325032</v>
+        <v>325240</v>
       </c>
       <c r="R8" t="n">
-        <v>6556777</v>
+        <v>6556535</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,12 +1408,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,34 +1422,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246640</t>
+          <t>https://artportalen.se/Sighting/136890271</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134246890</v>
+        <v>136890273</v>
       </c>
       <c r="B9" t="n">
-        <v>79992</v>
+        <v>93411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,40 +1456,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Svartetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>324955</v>
+        <v>325133</v>
       </c>
       <c r="R9" t="n">
-        <v>6556479</v>
+        <v>6556528</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1521,12 +1510,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,74 +1524,68 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246890</t>
+          <t>https://artportalen.se/Sighting/136890273</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136707324</v>
+        <v>136890274</v>
       </c>
       <c r="B10" t="n">
-        <v>4777</v>
+        <v>93411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325067</v>
+        <v>325119</v>
       </c>
       <c r="R10" t="n">
-        <v>6557022</v>
+        <v>6556525</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1629,12 +1612,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1645,21 +1628,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1675,56 +1643,51 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707324</t>
+          <t>https://artportalen.se/Sighting/136890274</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134493951</v>
+        <v>136890276</v>
       </c>
       <c r="B11" t="n">
-        <v>5181</v>
+        <v>93411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>325037</v>
+        <v>325102</v>
       </c>
       <c r="R11" t="n">
-        <v>6557099</v>
+        <v>6556509</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1751,12 +1714,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,21 +1730,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1797,63 +1745,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493951</t>
+          <t>https://artportalen.se/Sighting/136890276</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134246361</v>
+        <v>136890279</v>
       </c>
       <c r="B12" t="n">
-        <v>5484</v>
+        <v>93411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101920</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325037</v>
+        <v>325084</v>
       </c>
       <c r="R12" t="n">
-        <v>6556902</v>
+        <v>6556456</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1877,17 +1816,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,77 +1830,71 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246361</t>
+          <t>https://artportalen.se/Sighting/136890279</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134246677</v>
+        <v>136890281</v>
       </c>
       <c r="B13" t="n">
-        <v>5484</v>
+        <v>93411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101920</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325095</v>
+        <v>325044</v>
       </c>
       <c r="R13" t="n">
-        <v>6556772</v>
+        <v>6556448</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1990,17 +1918,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ett kläckhål i tallåga</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,77 +1932,71 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246677</t>
+          <t>https://artportalen.se/Sighting/136890281</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134246697</v>
+        <v>136890283</v>
       </c>
       <c r="B14" t="n">
-        <v>5484</v>
+        <v>93411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101920</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>325058</v>
+        <v>325030</v>
       </c>
       <c r="R14" t="n">
-        <v>6556688</v>
+        <v>6556403</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2103,17 +2020,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnagspån</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2122,34 +2034,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246697</t>
+          <t>https://artportalen.se/Sighting/136890283</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134246438</v>
+        <v>136890284</v>
       </c>
       <c r="B15" t="n">
-        <v>79396</v>
+        <v>93411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,48 +2068,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>260591</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>325044</v>
+        <v>325067</v>
       </c>
       <c r="R15" t="n">
-        <v>6556865</v>
+        <v>6556412</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2222,12 +2122,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,34 +2136,33 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246438</t>
+          <t>https://artportalen.se/Sighting/136890284</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134246734</v>
+        <v>136890288</v>
       </c>
       <c r="B16" t="n">
-        <v>79396</v>
+        <v>93411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2271,40 +2170,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>260591</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>325035</v>
+        <v>325082</v>
       </c>
       <c r="R16" t="n">
-        <v>6556559</v>
+        <v>6556321</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2328,17 +2224,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2347,23 +2238,2023 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890288</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136890272</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93449</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>325172</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6556503</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890272</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136890278</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93449</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>325077</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6556476</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890278</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136890282</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93449</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>325035</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6556443</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890282</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136890286</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93449</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>325093</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6556407</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890286</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134246367</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>325037</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6556902</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246367</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134246640</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>325032</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6556777</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246640</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134246890</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Svartetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>324955</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6556479</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246890</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136890277</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>325074</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6556468</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890277</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136890280</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>325060</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6556441</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890280</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136707324</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>325067</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6557022</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707324</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134493951</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>325037</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6557099</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134493951</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134246361</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5484</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>101920</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Raggbock</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tragosoma depsarium</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>325037</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6556902</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246361</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134246677</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5484</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>101920</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Raggbock</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tragosoma depsarium</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>325095</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6556772</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ett kläckhål i tallåga</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246677</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134246697</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5484</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>101920</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Raggbock</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tragosoma depsarium</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>325058</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6556688</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnagspån</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246697</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136890270</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>325256</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6556560</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890270</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136890285</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>325081</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6556421</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136890285</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134246438</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>325044</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6556865</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246438</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134246734</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>325035</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6556559</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134246734</t>
         </is>
@@ -2386,6 +4277,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2669,10 +2669,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134246367</v>
+        <v>136958358</v>
       </c>
       <c r="B21" t="n">
-        <v>79992</v>
+        <v>79233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2680,40 +2680,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>325037</v>
+        <v>325074</v>
       </c>
       <c r="R21" t="n">
-        <v>6556902</v>
+        <v>6556468</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2737,12 +2734,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2751,31 +2748,30 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246367</t>
+          <t>https://artportalen.se/Sighting/136958358</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134246640</v>
+        <v>134246367</v>
       </c>
       <c r="B22" t="n">
         <v>79992</v>
@@ -2813,10 +2809,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>325032</v>
+        <v>325037</v>
       </c>
       <c r="R22" t="n">
-        <v>6556777</v>
+        <v>6556902</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,13 +2871,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246640</t>
+          <t>https://artportalen.se/Sighting/134246367</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134246890</v>
+        <v>134246640</v>
       </c>
       <c r="B23" t="n">
         <v>79992</v>
@@ -2915,14 +2911,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Svartetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>324955</v>
+        <v>325032</v>
       </c>
       <c r="R23" t="n">
-        <v>6556479</v>
+        <v>6556777</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2981,16 +2977,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246890</t>
+          <t>https://artportalen.se/Sighting/134246640</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136890277</v>
+        <v>134246890</v>
       </c>
       <c r="B24" t="n">
-        <v>80095</v>
+        <v>79992</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3016,19 +3012,22 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mellanfjällen, Dls</t>
+          <t>Svartetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>325074</v>
+        <v>324955</v>
       </c>
       <c r="R24" t="n">
-        <v>6556468</v>
+        <v>6556479</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3052,12 +3051,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3066,45 +3065,31 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136890277</t>
+          <t>https://artportalen.se/Sighting/134246890</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136890280</v>
+        <v>136890277</v>
       </c>
       <c r="B25" t="n">
         <v>80095</v>
@@ -3139,10 +3124,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>325060</v>
+        <v>325074</v>
       </c>
       <c r="R25" t="n">
-        <v>6556441</v>
+        <v>6556468</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3186,6 +3171,21 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
@@ -3200,56 +3200,51 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136890280</t>
+          <t>https://artportalen.se/Sighting/136890277</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136707324</v>
+        <v>136890280</v>
       </c>
       <c r="B26" t="n">
-        <v>4777</v>
+        <v>80095</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100299</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>325067</v>
+        <v>325060</v>
       </c>
       <c r="R26" t="n">
-        <v>6557022</v>
+        <v>6556441</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3276,12 +3271,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3292,21 +3287,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3322,16 +3302,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707324</t>
+          <t>https://artportalen.se/Sighting/136890280</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134493951</v>
+        <v>136707324</v>
       </c>
       <c r="B27" t="n">
-        <v>5181</v>
+        <v>4777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3339,21 +3319,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3368,10 +3348,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>325037</v>
+        <v>325067</v>
       </c>
       <c r="R27" t="n">
-        <v>6557099</v>
+        <v>6557022</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3398,12 +3378,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3444,50 +3424,46 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134493951</t>
+          <t>https://artportalen.se/Sighting/136707324</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134246361</v>
+        <v>134493951</v>
       </c>
       <c r="B28" t="n">
-        <v>5484</v>
+        <v>5181</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101920</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -3497,10 +3473,10 @@
         <v>325037</v>
       </c>
       <c r="R28" t="n">
-        <v>6556902</v>
+        <v>6557099</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3524,17 +3500,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3543,31 +3514,45 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246361</t>
+          <t>https://artportalen.se/Sighting/134493951</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134246677</v>
+        <v>134246361</v>
       </c>
       <c r="B29" t="n">
         <v>5484</v>
@@ -3599,7 +3584,11 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3607,10 +3596,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>325095</v>
+        <v>325037</v>
       </c>
       <c r="R29" t="n">
-        <v>6556772</v>
+        <v>6556902</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3647,7 +3636,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ett kläckhål i tallåga</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,13 +3663,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246677</t>
+          <t>https://artportalen.se/Sighting/134246361</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134246697</v>
+        <v>134246677</v>
       </c>
       <c r="B30" t="n">
         <v>5484</v>
@@ -3720,10 +3709,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>325058</v>
+        <v>325095</v>
       </c>
       <c r="R30" t="n">
-        <v>6556688</v>
+        <v>6556772</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3760,7 +3749,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Kläckhål och gnagspån</t>
+          <t>Ett kläckhål i tallåga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3787,59 +3776,59 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246697</t>
+          <t>https://artportalen.se/Sighting/134246677</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136890270</v>
+        <v>134246697</v>
       </c>
       <c r="B31" t="n">
-        <v>8463</v>
+        <v>5484</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>101920</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>325256</v>
+        <v>325058</v>
       </c>
       <c r="R31" t="n">
-        <v>6556560</v>
+        <v>6556688</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3863,12 +3852,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnagspån</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3877,45 +3871,31 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136890270</t>
+          <t>https://artportalen.se/Sighting/134246697</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136890285</v>
+        <v>136890270</v>
       </c>
       <c r="B32" t="n">
         <v>8463</v>
@@ -3955,10 +3935,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>325081</v>
+        <v>325256</v>
       </c>
       <c r="R32" t="n">
-        <v>6556421</v>
+        <v>6556560</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4031,65 +4011,59 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136890285</t>
+          <t>https://artportalen.se/Sighting/136890270</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134246438</v>
+        <v>136890285</v>
       </c>
       <c r="B33" t="n">
-        <v>79396</v>
+        <v>8463</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>260591</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>325044</v>
+        <v>325081</v>
       </c>
       <c r="R33" t="n">
-        <v>6556865</v>
+        <v>6556421</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4113,12 +4087,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4127,31 +4101,45 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134246438</t>
+          <t>https://artportalen.se/Sighting/136890285</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134246734</v>
+        <v>134246438</v>
       </c>
       <c r="B34" t="n">
         <v>79396</v>
@@ -4179,8 +4167,16 @@
           <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4189,10 +4185,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>325035</v>
+        <v>325044</v>
       </c>
       <c r="R34" t="n">
-        <v>6556559</v>
+        <v>6556865</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4227,11 +4223,6 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4255,6 +4246,117 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134246438</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134246734</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>325035</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6556559</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134246734</t>
         </is>
@@ -4295,6 +4397,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>136890275</v>
       </c>
       <c r="B3" t="n">
-        <v>90859</v>
+        <v>90861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>136890271</v>
       </c>
       <c r="B8" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136890273</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>136890274</v>
       </c>
       <c r="B10" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136890276</v>
       </c>
       <c r="B11" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136890279</v>
       </c>
       <c r="B12" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136890281</v>
       </c>
       <c r="B13" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890283</v>
       </c>
       <c r="B14" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890284</v>
       </c>
       <c r="B15" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890288</v>
       </c>
       <c r="B16" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890272</v>
       </c>
       <c r="B17" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890278</v>
       </c>
       <c r="B18" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136890282</v>
       </c>
       <c r="B19" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>136890286</v>
       </c>
       <c r="B20" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>136958358</v>
       </c>
       <c r="B21" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>136890277</v>
       </c>
       <c r="B25" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>136890280</v>
       </c>
       <c r="B26" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>136890275</v>
       </c>
       <c r="B3" t="n">
-        <v>90861</v>
+        <v>90863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>136890271</v>
       </c>
       <c r="B8" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136890273</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>136890274</v>
       </c>
       <c r="B10" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136890276</v>
       </c>
       <c r="B11" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136890279</v>
       </c>
       <c r="B12" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136890281</v>
       </c>
       <c r="B13" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890283</v>
       </c>
       <c r="B14" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890284</v>
       </c>
       <c r="B15" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890288</v>
       </c>
       <c r="B16" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890272</v>
       </c>
       <c r="B17" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890278</v>
       </c>
       <c r="B18" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136890282</v>
       </c>
       <c r="B19" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>136890286</v>
       </c>
       <c r="B20" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>136958358</v>
       </c>
       <c r="B21" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>136890277</v>
       </c>
       <c r="B25" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>136890280</v>
       </c>
       <c r="B26" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -3433,7 +3433,7 @@
         <v>134493951</v>
       </c>
       <c r="B28" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>136890275</v>
       </c>
       <c r="B3" t="n">
-        <v>90863</v>
+        <v>90864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>136890271</v>
       </c>
       <c r="B8" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136890273</v>
       </c>
       <c r="B9" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>136890274</v>
       </c>
       <c r="B10" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136890276</v>
       </c>
       <c r="B11" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136890279</v>
       </c>
       <c r="B12" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136890281</v>
       </c>
       <c r="B13" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890283</v>
       </c>
       <c r="B14" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890284</v>
       </c>
       <c r="B15" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890288</v>
       </c>
       <c r="B16" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890272</v>
       </c>
       <c r="B17" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890278</v>
       </c>
       <c r="B18" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136890282</v>
       </c>
       <c r="B19" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>136890286</v>
       </c>
       <c r="B20" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>136958358</v>
       </c>
       <c r="B21" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>136890277</v>
       </c>
       <c r="B25" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>136890280</v>
       </c>
       <c r="B26" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>136890275</v>
       </c>
       <c r="B3" t="n">
-        <v>90864</v>
+        <v>90870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>136890271</v>
       </c>
       <c r="B8" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136890273</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>136890274</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136890276</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136890279</v>
       </c>
       <c r="B12" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136890281</v>
       </c>
       <c r="B13" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890283</v>
       </c>
       <c r="B14" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890284</v>
       </c>
       <c r="B15" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890288</v>
       </c>
       <c r="B16" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890272</v>
       </c>
       <c r="B17" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890278</v>
       </c>
       <c r="B18" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136890282</v>
       </c>
       <c r="B19" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>136890286</v>
       </c>
       <c r="B20" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>136890275</v>
       </c>
       <c r="B3" t="n">
-        <v>90870</v>
+        <v>90874</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>136890271</v>
       </c>
       <c r="B8" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136890273</v>
       </c>
       <c r="B9" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>136890274</v>
       </c>
       <c r="B10" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136890276</v>
       </c>
       <c r="B11" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136890279</v>
       </c>
       <c r="B12" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136890281</v>
       </c>
       <c r="B13" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890283</v>
       </c>
       <c r="B14" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890284</v>
       </c>
       <c r="B15" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890288</v>
       </c>
       <c r="B16" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890272</v>
       </c>
       <c r="B17" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890278</v>
       </c>
       <c r="B18" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136890282</v>
       </c>
       <c r="B19" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>136890286</v>
       </c>
       <c r="B20" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>136958358</v>
       </c>
       <c r="B21" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>136890277</v>
       </c>
       <c r="B25" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>136890280</v>
       </c>
       <c r="B26" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>136890275</v>
       </c>
       <c r="B3" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>136890271</v>
       </c>
       <c r="B8" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136890273</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>136890274</v>
       </c>
       <c r="B10" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136890276</v>
       </c>
       <c r="B11" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136890279</v>
       </c>
       <c r="B12" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136890281</v>
       </c>
       <c r="B13" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890283</v>
       </c>
       <c r="B14" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890284</v>
       </c>
       <c r="B15" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890288</v>
       </c>
       <c r="B16" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890272</v>
       </c>
       <c r="B17" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890278</v>
       </c>
       <c r="B18" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136890282</v>
       </c>
       <c r="B19" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>136890286</v>
       </c>
       <c r="B20" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>136958358</v>
       </c>
       <c r="B21" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>136890277</v>
       </c>
       <c r="B25" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>136890280</v>
       </c>
       <c r="B26" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>136890275</v>
       </c>
       <c r="B3" t="n">
-        <v>90876</v>
+        <v>90889</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>136890271</v>
       </c>
       <c r="B8" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136890273</v>
       </c>
       <c r="B9" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>136890274</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136890276</v>
       </c>
       <c r="B11" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136890279</v>
       </c>
       <c r="B12" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136890281</v>
       </c>
       <c r="B13" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890283</v>
       </c>
       <c r="B14" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890284</v>
       </c>
       <c r="B15" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890288</v>
       </c>
       <c r="B16" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890272</v>
       </c>
       <c r="B17" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890278</v>
       </c>
       <c r="B18" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136890282</v>
       </c>
       <c r="B19" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>136890286</v>
       </c>
       <c r="B20" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>136958358</v>
       </c>
       <c r="B21" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>136890277</v>
       </c>
       <c r="B25" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>136890280</v>
       </c>
       <c r="B26" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>136890275</v>
       </c>
       <c r="B3" t="n">
-        <v>90889</v>
+        <v>90891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>136890271</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136890273</v>
       </c>
       <c r="B9" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>136890274</v>
       </c>
       <c r="B10" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136890276</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136890279</v>
       </c>
       <c r="B12" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136890281</v>
       </c>
       <c r="B13" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890283</v>
       </c>
       <c r="B14" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890284</v>
       </c>
       <c r="B15" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890288</v>
       </c>
       <c r="B16" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890272</v>
       </c>
       <c r="B17" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890278</v>
       </c>
       <c r="B18" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136890282</v>
       </c>
       <c r="B19" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>136890286</v>
       </c>
       <c r="B20" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>136958358</v>
       </c>
       <c r="B21" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>136890277</v>
       </c>
       <c r="B25" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>136890280</v>
       </c>
       <c r="B26" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>136890270</v>
       </c>
       <c r="B32" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>136890285</v>
       </c>
       <c r="B33" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -3337,11 +3337,7 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -3459,11 +3455,7 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -3924,11 +3916,7 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -4046,11 +4034,7 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>136890275</v>
       </c>
       <c r="B3" t="n">
-        <v>90891</v>
+        <v>90894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>136890271</v>
       </c>
       <c r="B8" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136890273</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>136890274</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136890276</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136890279</v>
       </c>
       <c r="B12" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136890281</v>
       </c>
       <c r="B13" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890283</v>
       </c>
       <c r="B14" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890284</v>
       </c>
       <c r="B15" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890288</v>
       </c>
       <c r="B16" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890272</v>
       </c>
       <c r="B17" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890278</v>
       </c>
       <c r="B18" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136890282</v>
       </c>
       <c r="B19" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>136890286</v>
       </c>
       <c r="B20" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>136890275</v>
       </c>
       <c r="B3" t="n">
-        <v>90894</v>
+        <v>90904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>136890271</v>
       </c>
       <c r="B8" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136890273</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>136890274</v>
       </c>
       <c r="B10" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136890276</v>
       </c>
       <c r="B11" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136890279</v>
       </c>
       <c r="B12" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136890281</v>
       </c>
       <c r="B13" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890283</v>
       </c>
       <c r="B14" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890284</v>
       </c>
       <c r="B15" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890288</v>
       </c>
       <c r="B16" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890272</v>
       </c>
       <c r="B17" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890278</v>
       </c>
       <c r="B18" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136890282</v>
       </c>
       <c r="B19" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>136890286</v>
       </c>
       <c r="B20" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>136958358</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>136890277</v>
       </c>
       <c r="B25" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>136890280</v>
       </c>
       <c r="B26" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>136707324</v>
       </c>
       <c r="B27" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>134493951</v>
       </c>
       <c r="B28" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>136890270</v>
       </c>
       <c r="B32" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>136890285</v>
       </c>
       <c r="B33" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>136890275</v>
       </c>
       <c r="B3" t="n">
-        <v>90904</v>
+        <v>90905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>136890271</v>
       </c>
       <c r="B8" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136890273</v>
       </c>
       <c r="B9" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>136890274</v>
       </c>
       <c r="B10" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136890276</v>
       </c>
       <c r="B11" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136890279</v>
       </c>
       <c r="B12" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136890281</v>
       </c>
       <c r="B13" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890283</v>
       </c>
       <c r="B14" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890284</v>
       </c>
       <c r="B15" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890288</v>
       </c>
       <c r="B16" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890272</v>
       </c>
       <c r="B17" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890278</v>
       </c>
       <c r="B18" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136890282</v>
       </c>
       <c r="B19" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>136890286</v>
       </c>
       <c r="B20" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>136890275</v>
       </c>
       <c r="B3" t="n">
-        <v>90905</v>
+        <v>90908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>136890271</v>
       </c>
       <c r="B8" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136890273</v>
       </c>
       <c r="B9" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>136890274</v>
       </c>
       <c r="B10" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136890276</v>
       </c>
       <c r="B11" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136890279</v>
       </c>
       <c r="B12" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136890281</v>
       </c>
       <c r="B13" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890283</v>
       </c>
       <c r="B14" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890284</v>
       </c>
       <c r="B15" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890288</v>
       </c>
       <c r="B16" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890272</v>
       </c>
       <c r="B17" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890278</v>
       </c>
       <c r="B18" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136890282</v>
       </c>
       <c r="B19" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>136890286</v>
       </c>
       <c r="B20" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>136958358</v>
       </c>
       <c r="B21" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>136890277</v>
       </c>
       <c r="B25" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>136890280</v>
       </c>
       <c r="B26" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 22922-2026 artfynd.xlsx
+++ b/artfynd/A 22922-2026 artfynd.xlsx
@@ -1346,7 +1346,7 @@
         <v>136890271</v>
       </c>
       <c r="B8" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>136890273</v>
       </c>
       <c r="B9" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>136890274</v>
       </c>
       <c r="B10" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136890276</v>
       </c>
       <c r="B11" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>136890279</v>
       </c>
       <c r="B12" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136890281</v>
       </c>
       <c r="B13" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>136890283</v>
       </c>
       <c r="B14" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>136890284</v>
       </c>
       <c r="B15" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>136890288</v>
       </c>
       <c r="B16" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136890272</v>
       </c>
       <c r="B17" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>136890278</v>
       </c>
       <c r="B18" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>136890282</v>
       </c>
       <c r="B19" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>136890286</v>
       </c>
       <c r="B20" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
